--- a/Data/Grupos.xlsx
+++ b/Data/Grupos.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bancolombia-my.sharepoint.com/personal/damonsal_bancolombia_com_co/Documents/Reto_mundial/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5408DEE9-9274-48B6-8E9D-3D7F94E9EC1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{5408DEE9-9274-48B6-8E9D-3D7F94E9EC1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5767F78-4A44-4AD4-B60E-B361115AB7C8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{13E7EB45-29C3-417E-B697-42D239005575}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$B$65</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="87">
   <si>
     <t>Grupo D</t>
   </si>
@@ -206,9 +209,6 @@
     <t>Turquía</t>
   </si>
   <si>
-    <t>Play-off UEFA (Ruta C: vs Rumania/Eslovaquia/Kosovo)</t>
-  </si>
-  <si>
     <t>Ucrania</t>
   </si>
   <si>
@@ -264,9 +264,6 @@
   </si>
   <si>
     <t>DR Congo</t>
-  </si>
-  <si>
-    <t>Repechaje Intercontinental (vs Jamaica/N. Caledonia)</t>
   </si>
   <si>
     <t>Iraq</t>
@@ -337,19 +334,15 @@
       <t xml:space="preserve"> (Anfitrión)</t>
     </r>
   </si>
+  <si>
+    <t>Suecia</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -395,10 +388,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -733,7 +726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC74F0DE-D6BA-4A1C-AAB2-DB1D893CE5C4}">
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.90625" bestFit="1" customWidth="1"/>
@@ -742,215 +735,215 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>86</v>
+      <c r="A3" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>87</v>
+      <c r="A4" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
+      <c r="A7" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>11</v>
+      <c r="A9" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
-        <v>21</v>
+      <c r="A14" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
-        <v>24</v>
+      <c r="A17" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>20</v>
@@ -958,31 +951,31 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>10</v>
@@ -990,71 +983,71 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" s="2" t="s">
-        <v>41</v>
+      <c r="A34" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" s="2" t="s">
-        <v>45</v>
+      <c r="A38" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>4</v>
@@ -1062,7 +1055,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>4</v>
@@ -1070,189 +1063,202 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" s="1" t="s">
-        <v>51</v>
+      <c r="A44" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" s="1" t="s">
-        <v>55</v>
+      <c r="A46" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>58</v>
+      <c r="A47" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A48" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>60</v>
+      <c r="A48" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>62</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A60" s="2" t="s">
-        <v>77</v>
+      <c r="A60" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A61" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>78</v>
+      <c r="A61" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B65" xr:uid="{FC74F0DE-D6BA-4A1C-AAB2-DB1D893CE5C4}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B65">
+      <sortCondition ref="B1:B65"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>